--- a/data/historial/2026-07-16.xlsx
+++ b/data/historial/2026-07-16.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\OneDrive\Desktop\Reportes Ventas Rap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{792E26D5-7F37-4AE3-ADDF-CBF926AC22BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9662770-FF61-4206-A90A-8C64C34915B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="COMISIONES" sheetId="7" r:id="rId1"/>
@@ -27657,7 +27657,7 @@
       </c>
       <c r="C2" s="133"/>
       <c r="D2" s="133">
-        <v>0.15071662808641975</v>
+        <v>0.14865001286008231</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -27670,7 +27670,7 @@
       </c>
       <c r="C3" s="133"/>
       <c r="D3" s="133">
-        <v>0.26634870113168718</v>
+        <v>0.26052887088477367</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -27683,7 +27683,7 @@
       </c>
       <c r="C4" s="133"/>
       <c r="D4" s="133">
-        <v>0.22999903549382714</v>
+        <v>0.22935731738683127</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -27696,7 +27696,7 @@
       </c>
       <c r="C5" s="133"/>
       <c r="D5" s="133">
-        <v>0.23246945730452676</v>
+        <v>0.22475597993827159</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -27709,7 +27709,7 @@
       </c>
       <c r="C6" s="133"/>
       <c r="D6" s="133">
-        <v>0.20460808899176955</v>
+        <v>0.19312596450617284</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -27722,7 +27722,7 @@
       </c>
       <c r="C7" s="133"/>
       <c r="D7" s="133">
-        <v>0.2486332947530864</v>
+        <v>0.23779288837448562</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -27735,7 +27735,7 @@
       </c>
       <c r="C8" s="133"/>
       <c r="D8" s="133">
-        <v>0.22467399691358025</v>
+        <v>0.22402134773662552</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -27748,7 +27748,7 @@
       </c>
       <c r="C9" s="133"/>
       <c r="D9" s="133">
-        <v>0.22230613425925927</v>
+        <v>0.212401941872428</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -27761,7 +27761,7 @@
       </c>
       <c r="C10" s="133"/>
       <c r="D10" s="133">
-        <v>8.7914094650205762E-2</v>
+        <v>9.1671810699588477E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -27774,7 +27774,7 @@
       </c>
       <c r="C11" s="133"/>
       <c r="D11" s="133">
-        <v>0.2383159722222222</v>
+        <v>0.23162358539094652</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -27787,7 +27787,7 @@
       </c>
       <c r="C12" s="133"/>
       <c r="D12" s="133">
-        <v>0.27321116255144035</v>
+        <v>0.26401748971193417</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -27800,7 +27800,7 @@
       </c>
       <c r="C13" s="133"/>
       <c r="D13" s="133">
-        <v>0.23825810185185176</v>
+        <v>0.22885995370370363</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -27813,7 +27813,7 @@
       </c>
       <c r="C14" s="133"/>
       <c r="D14" s="133">
-        <v>0.27006301440329217</v>
+        <v>0.25927147633744857</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -27826,7 +27826,7 @@
       </c>
       <c r="C15" s="133"/>
       <c r="D15" s="133">
-        <v>0.22656957304526748</v>
+        <v>0.22336676954732512</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -27839,7 +27839,7 @@
       </c>
       <c r="C16" s="133"/>
       <c r="D16" s="133">
-        <v>0.22884548611111113</v>
+        <v>0.22607156635802472</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -27852,7 +27852,7 @@
       </c>
       <c r="C17" s="133"/>
       <c r="D17" s="133">
-        <v>0.24085455246913581</v>
+        <v>0.23726723251028806</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -27865,7 +27865,7 @@
       </c>
       <c r="C18" s="133"/>
       <c r="D18" s="133">
-        <v>0.25471675668724281</v>
+        <v>0.24185088734567906</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -27878,7 +27878,7 @@
       </c>
       <c r="C19" s="133"/>
       <c r="D19" s="133">
-        <v>0.24575713734567897</v>
+        <v>0.23289126800411522</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -27891,7 +27891,7 @@
       </c>
       <c r="C20" s="133"/>
       <c r="D20" s="133">
-        <v>0.28491030092592595</v>
+        <v>0.27809059927983543</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -27904,7 +27904,7 @@
       </c>
       <c r="C21" s="133"/>
       <c r="D21" s="133">
-        <v>0.23830761316872429</v>
+        <v>0.23471579218106997</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -27917,7 +27917,7 @@
       </c>
       <c r="C22" s="133"/>
       <c r="D22" s="133">
-        <v>0.23375578703703703</v>
+        <v>0.22338284465020575</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -27930,7 +27930,7 @@
       </c>
       <c r="C23" s="133"/>
       <c r="D23" s="133">
-        <v>0.20357960390946506</v>
+        <v>0.20604809670781896</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -27943,7 +27943,7 @@
       </c>
       <c r="C24" s="133"/>
       <c r="D24" s="133">
-        <v>0.26268164866255145</v>
+        <v>0.25543756430041148</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -27956,7 +27956,7 @@
       </c>
       <c r="C25" s="133"/>
       <c r="D25" s="133">
-        <v>0.19930073302469142</v>
+        <v>0.19253632973251034</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -27969,7 +27969,7 @@
       </c>
       <c r="C26" s="133"/>
       <c r="D26" s="133">
-        <v>0.23281764403292185</v>
+        <v>0.2249672067901235</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -27982,7 +27982,7 @@
       </c>
       <c r="C27" s="133"/>
       <c r="D27" s="133">
-        <v>0.23525655864197528</v>
+        <v>0.23259259259259257</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -27995,7 +27995,7 @@
       </c>
       <c r="C28" s="133"/>
       <c r="D28" s="133">
-        <v>0.26416087962962953</v>
+        <v>0.24269290123456785</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -28008,7 +28008,7 @@
       </c>
       <c r="C29" s="133"/>
       <c r="D29" s="133">
-        <v>0.19831886574074076</v>
+        <v>0.19584008487654322</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -28021,7 +28021,7 @@
       </c>
       <c r="C30" s="133"/>
       <c r="D30" s="133">
-        <v>0.19230002572016466</v>
+        <v>0.18343364197530868</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -28034,7 +28034,7 @@
       </c>
       <c r="C31" s="133"/>
       <c r="D31" s="133">
-        <v>0.17871849279835392</v>
+        <v>0.17957497427983538</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -28047,7 +28047,7 @@
       </c>
       <c r="C32" s="133"/>
       <c r="D32" s="133">
-        <v>0.1781458976337448</v>
+        <v>0.18009227109053494</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -28060,7 +28060,7 @@
       </c>
       <c r="C33" s="133"/>
       <c r="D33" s="133">
-        <v>0.1792975180041152</v>
+        <v>0.17969939557613168</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -28073,7 +28073,7 @@
       </c>
       <c r="C34" s="133"/>
       <c r="D34" s="133">
-        <v>0.11472961676954729</v>
+        <v>0.10784304269547323</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -28086,7 +28086,7 @@
       </c>
       <c r="C35" s="133"/>
       <c r="D35" s="133">
-        <v>0.11771797839506172</v>
+        <v>0.11119984567901235</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">

--- a/data/historial/2026-07-16.xlsx
+++ b/data/historial/2026-07-16.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\OneDrive\Desktop\Reportes Ventas Rap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9662770-FF61-4206-A90A-8C64C34915B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E040891-BCA1-43AC-9E9C-5B27C6574292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="COMISIONES" sheetId="7" r:id="rId1"/>
@@ -2848,13 +2848,13 @@
         <v>0</v>
       </c>
       <c r="C2" s="153">
-        <v>57477.4827570696</v>
+        <v>57481.822042783802</v>
       </c>
       <c r="D2" s="153">
-        <v>292519.6825286391</v>
+        <v>292519.9350286391</v>
       </c>
       <c r="E2" s="153">
-        <v>998440578.42036676</v>
+        <v>998556474.18880832</v>
       </c>
       <c r="F2" s="153">
         <v>0</v>
@@ -3524,13 +3524,13 @@
         <v>1</v>
       </c>
       <c r="C28" s="153">
-        <v>791.29948412390002</v>
+        <v>795.88876983809996</v>
       </c>
       <c r="D28" s="153">
-        <v>2775.2176666691998</v>
+        <v>2775.4701666691999</v>
       </c>
       <c r="E28" s="153">
-        <v>16424552.675492924</v>
+        <v>16562384.885934453</v>
       </c>
       <c r="F28" s="153">
         <v>0</v>
@@ -3576,13 +3576,13 @@
         <v>1</v>
       </c>
       <c r="C30" s="153">
-        <v>287.41494047499998</v>
+        <v>287.16494047499998</v>
       </c>
       <c r="D30" s="153">
         <v>1152.8863452348</v>
       </c>
       <c r="E30" s="153">
-        <v>6739738.9934741603</v>
+        <v>6717802.5514741596</v>
       </c>
       <c r="F30" s="153">
         <v>0</v>
@@ -3784,13 +3784,13 @@
         <v>1</v>
       </c>
       <c r="C38" s="153">
-        <v>20.999999999700002</v>
+        <v>1020.9999999997</v>
       </c>
       <c r="D38" s="153">
-        <v>-6214.4500000035996</v>
+        <v>10885.549999996399</v>
       </c>
       <c r="E38" s="153">
-        <v>-8621894.4787910581</v>
+        <v>24551080.766208943</v>
       </c>
       <c r="F38" s="153">
         <v>0</v>
@@ -4018,13 +4018,13 @@
         <v>1</v>
       </c>
       <c r="C47" s="153">
-        <v>2074.6438888887001</v>
+        <v>1074.6438888887001</v>
       </c>
       <c r="D47" s="153">
-        <v>20788.654202383601</v>
+        <v>3688.6542023836</v>
       </c>
       <c r="E47" s="153">
-        <v>49828762.744359016</v>
+        <v>16655787.499359019</v>
       </c>
       <c r="F47" s="153">
         <v>0</v>
@@ -14169,38 +14169,38 @@
       </c>
       <c r="D13" s="4">
         <f>IFERROR(+VLOOKUP(B13,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>-8621894.4787910581</v>
+        <v>24551080.766208943</v>
       </c>
       <c r="E13" s="4">
         <v>22023211.318708941</v>
       </c>
       <c r="F13" s="59">
         <f t="shared" si="6"/>
-        <v>-30645105.797499999</v>
+        <v>2527869.4475000016</v>
       </c>
       <c r="G13" s="5">
         <f t="shared" si="1"/>
-        <v>-0.20311156496520213</v>
+        <v>0.57836574644682759</v>
       </c>
       <c r="H13" s="4">
         <f t="shared" si="4"/>
-        <v>-17243788.957582116</v>
+        <v>49102161.532417886</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="2"/>
-        <v>-0.40622312993040427</v>
+        <v>1.1567314928936552</v>
       </c>
       <c r="J13" s="4">
         <f t="shared" si="5"/>
-        <v>-663222.65221469675</v>
+        <v>1888544.6743237649</v>
       </c>
       <c r="K13" s="4">
         <f t="shared" si="3"/>
-        <v>3928534.759520466</v>
+        <v>1376767.4329820042</v>
       </c>
       <c r="L13" s="63" cm="1">
         <f t="array" ref="L13">+_xlfn.IFS(I13&gt;109%,H13*0.015,I13&gt;104%,H13*0.0125,I13&gt;99%,H13*0.01,I13&lt;99%,H13*0)</f>
-        <v>0</v>
+        <v>736532.4229862683</v>
       </c>
       <c r="N13" s="28"/>
     </row>
@@ -14256,34 +14256,34 @@
       </c>
       <c r="D15" s="64">
         <f>+SUM(D11:D14)</f>
-        <v>165841921.86489576</v>
+        <v>199014897.10989577</v>
       </c>
       <c r="E15" s="65">
         <v>191588262.20906579</v>
       </c>
       <c r="F15" s="67">
         <f>+D15-E15</f>
-        <v>-25746340.344170034</v>
+        <v>7426634.9008299708</v>
       </c>
       <c r="G15" s="66">
         <f t="shared" si="1"/>
-        <v>0.48510955853190629</v>
+        <v>0.58214489914621548</v>
       </c>
       <c r="H15" s="64">
         <f t="shared" si="4"/>
-        <v>331683843.72979152</v>
+        <v>398029794.21979153</v>
       </c>
       <c r="I15" s="66">
         <f t="shared" si="2"/>
-        <v>0.97021911706381259</v>
+        <v>1.164289798292431</v>
       </c>
       <c r="J15" s="64">
         <f t="shared" si="5"/>
-        <v>12757070.91268429</v>
+        <v>15308838.239222752</v>
       </c>
       <c r="K15" s="67">
         <f t="shared" si="3"/>
-        <v>13540227.683721827</v>
+        <v>10988460.357183365</v>
       </c>
       <c r="L15" s="68"/>
     </row>
@@ -14519,38 +14519,38 @@
       </c>
       <c r="D21" s="4">
         <f>IFERROR(+VLOOKUP(B21,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>16424552.675492924</v>
+        <v>16562384.885934453</v>
       </c>
       <c r="E21" s="4">
         <v>14684129.439204972</v>
       </c>
       <c r="F21" s="59">
         <f t="shared" si="7"/>
-        <v>1740423.2362879515</v>
+        <v>1878255.4467294812</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="1"/>
-        <v>0.50382063421757439</v>
+        <v>0.50804861613295871</v>
       </c>
       <c r="H21" s="4">
         <f t="shared" si="4"/>
-        <v>32849105.350985847</v>
+        <v>33124769.771868907</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="2"/>
-        <v>1.0076412684351488</v>
+        <v>1.0160972322659174</v>
       </c>
       <c r="J21" s="4">
         <f t="shared" si="5"/>
-        <v>1263427.128884071</v>
+        <v>1274029.6066103426</v>
       </c>
       <c r="K21" s="4">
         <f t="shared" si="3"/>
-        <v>1244265.1788082367</v>
+        <v>1233662.7010819651</v>
       </c>
       <c r="L21" s="63" cm="1">
         <f t="array" ref="L21">+_xlfn.IFS(I21&gt;114%,H21*0.02,I21&gt;109%,H21*0.015,I21&gt;104%,H21*0.0125,I21&gt;99%,H21*0.01,I21&lt;99%,H21*0)</f>
-        <v>328491.0535098585</v>
+        <v>331247.6977186891</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -14649,34 +14649,34 @@
       </c>
       <c r="D24" s="67">
         <f>+SUM(D16:D23)</f>
-        <v>123634921.72097193</v>
+        <v>123772753.93141346</v>
       </c>
       <c r="E24" s="65">
         <v>113342982.9620823</v>
       </c>
       <c r="F24" s="67">
         <f>+D24-E24</f>
-        <v>10291938.75888963</v>
+        <v>10429770.96933116</v>
       </c>
       <c r="G24" s="66">
         <f t="shared" si="1"/>
-        <v>0.52028330480567242</v>
+        <v>0.52086333346552816</v>
       </c>
       <c r="H24" s="64">
         <f t="shared" si="4"/>
-        <v>247269843.44194388</v>
+        <v>247545507.86282694</v>
       </c>
       <c r="I24" s="66">
         <f t="shared" si="2"/>
-        <v>1.0405666096113448</v>
+        <v>1.0417266669310565</v>
       </c>
       <c r="J24" s="64">
         <f t="shared" si="5"/>
-        <v>9510378.5939209182</v>
+        <v>9520981.0716471896</v>
       </c>
       <c r="K24" s="67">
         <f t="shared" si="3"/>
-        <v>8768852.1753098518</v>
+        <v>8758249.6975835804</v>
       </c>
       <c r="L24" s="68"/>
     </row>
@@ -15004,34 +15004,34 @@
       </c>
       <c r="D32" s="4">
         <f>IFERROR(+VLOOKUP(B32,COMISIONES!A:E,5,FALSE),"0")*1</f>
-        <v>6739738.9934741603</v>
+        <v>6717802.5514741596</v>
       </c>
       <c r="E32" s="4">
         <v>6135579.6092607612</v>
       </c>
       <c r="F32" s="59">
         <f t="shared" si="7"/>
-        <v>604159.38421339914</v>
+        <v>582222.9422133984</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="1"/>
-        <v>0.31311214836116896</v>
+        <v>0.31209303375025138</v>
       </c>
       <c r="H32" s="4">
         <f t="shared" si="4"/>
-        <v>13479477.986948321</v>
+        <v>13435605.102948319</v>
       </c>
       <c r="I32" s="5">
         <f t="shared" si="2"/>
-        <v>0.62622429672233793</v>
+        <v>0.62418606750050276</v>
       </c>
       <c r="J32" s="4">
         <f t="shared" si="5"/>
-        <v>518441.46103647386</v>
+        <v>516754.04242108919</v>
       </c>
       <c r="K32" s="4">
         <f t="shared" si="3"/>
-        <v>1137327.7697327568</v>
+        <v>1139015.1883481413</v>
       </c>
       <c r="L32" s="63" cm="1">
         <f t="array" ref="L32">+_xlfn.IFS(I32&gt;114%,H32*0.02,I32&gt;109%,H32*0.015,I32&gt;104%,H32*0.0125,I32&gt;99%,H32*0.01,I32&lt;99%,H32*0)</f>
@@ -15266,34 +15266,34 @@
       </c>
       <c r="D38" s="67">
         <f>+SUM(D25:D37)</f>
-        <v>187871146.97784558</v>
+        <v>187849210.53584558</v>
       </c>
       <c r="E38" s="65">
         <v>182030086.49221137</v>
       </c>
       <c r="F38" s="67">
         <f>+D38-E38</f>
-        <v>5841060.4856342077</v>
+        <v>5819124.0436342061</v>
       </c>
       <c r="G38" s="66">
         <f t="shared" si="1"/>
-        <v>0.36007561466186888</v>
+        <v>0.36003357106995115</v>
       </c>
       <c r="H38" s="64">
         <f t="shared" si="4"/>
-        <v>375742293.95569116</v>
+        <v>375698421.07169116</v>
       </c>
       <c r="I38" s="66">
         <f t="shared" si="2"/>
-        <v>0.72015122932373776</v>
+        <v>0.72006714213990231</v>
       </c>
       <c r="J38" s="64">
         <f t="shared" si="5"/>
-        <v>14451626.690603506</v>
+        <v>14449939.271988122</v>
       </c>
       <c r="K38" s="67">
         <f t="shared" si="3"/>
-        <v>25683350.803427551</v>
+        <v>25685038.222042937</v>
       </c>
       <c r="L38" s="68"/>
     </row>
@@ -15656,34 +15656,34 @@
       </c>
       <c r="D47" s="78">
         <f>+D38+D24+D10+D15+D46</f>
-        <v>838656201.17677879</v>
+        <v>871945072.19022036</v>
       </c>
       <c r="E47" s="79">
         <v>815884008.14172602</v>
       </c>
       <c r="F47" s="78">
         <f>+D47-E47</f>
-        <v>22772193.035052776</v>
+        <v>56061064.048494339</v>
       </c>
       <c r="G47" s="80">
         <f>+D47/C47</f>
-        <v>0.60782444555491977</v>
+        <v>0.63195088680522338</v>
       </c>
       <c r="H47" s="78">
         <f>+D47/$N$3*$N$4</f>
-        <v>1677312402.3535576</v>
+        <v>1743890144.3804407</v>
       </c>
       <c r="I47" s="142">
         <f t="shared" si="2"/>
-        <v>1.2156488911098395</v>
+        <v>1.2639017736104468</v>
       </c>
       <c r="J47" s="78">
         <f>+D47/$N$3</f>
-        <v>64512015.475136831</v>
+        <v>67072697.860786185</v>
       </c>
       <c r="K47" s="78">
         <f>+(C47-D47)/$N$2</f>
-        <v>41623918.916642867</v>
+        <v>39063236.530993514</v>
       </c>
       <c r="L47" s="81"/>
     </row>
